--- a/面数分布_明細.xlsx
+++ b/面数分布_明細.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +78,11 @@
         <fgColor rgb="00DFF0D8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -105,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,6 +138,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -500,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -510,6 +518,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>束縛形態素(vocabMetricExcluded)は語彙点の母数から除外。0面＝どの面にも問題が無い語／1面・2面＝下記の面だけ問題がある語。</t>
+          <t>H/I=聞き取り以外で作れる問題案。2026-08-28: カタカナ外来語83語に表記(カタカナ)を作問しcontent反映済み(→3面・緑)。指示語/感動詞/かな接辞は非一意等で作れず据え置き。</t>
         </is>
       </c>
     </row>
@@ -562,6 +572,16 @@
           <t>ある面（この面だけ問題がある）</t>
         </is>
       </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>作れる面(聞き取り除く)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>問題案／作れない理由</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -599,6 +619,16 @@
           <t>（なし＝0面）</t>
         </is>
       </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>△漢字読み・表記</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>熟語なら読みは問えるが接辞単独ゆえ薄い。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -636,6 +666,16 @@
           <t>（なし＝0面）</t>
         </is>
       </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>△漢字読み・表記</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>熟語で可:「山田君」→くん（薄い）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -673,6 +713,16 @@
           <t>（なし＝0面）</t>
         </is>
       </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>△漢字読み・表記</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>熟語で可:「人生観」→かん（薄い）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -710,6 +760,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -747,6 +807,16 @@
           <t>言い換え</t>
         </is>
       </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -784,6 +854,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -821,6 +901,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -858,6 +948,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -895,6 +995,16 @@
           <t>産出(語彙パズル)</t>
         </is>
       </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>接続/助詞＝単独作問不可。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -932,6 +1042,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -969,6 +1089,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1006,6 +1136,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>△漢字読み・表記</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>熟語で可:「三月 に 生まれた」→さんがつ／ひと月→（薄い）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1043,6 +1183,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1080,6 +1230,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1117,6 +1277,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1154,6 +1324,16 @@
           <t>聞き取り</t>
         </is>
       </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1191,6 +1371,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1228,6 +1418,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>△漢字読み・表記</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>熟語で可:「御住所」→ご（接頭・薄い）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1265,6 +1465,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>△漢字読み・表記</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>熟語で可:「本町」→ちょう（薄い）</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -1302,6 +1512,16 @@
           <t>聞き取り</t>
         </is>
       </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>助詞（1拍）＝作問不可。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1339,6 +1559,16 @@
           <t>文脈規定</t>
         </is>
       </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>△漢字読み・表記</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>熟語で可:「一敗」→ぱい（薄い）</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -1376,6 +1606,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1413,6 +1653,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -1420,9 +1670,9 @@
           <t>N5</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1448,6 +1698,16 @@
       <c r="G28" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -1457,9 +1717,9 @@
           <t>N5</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1485,6 +1745,16 @@
       <c r="G29" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -1524,6 +1794,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -1561,6 +1841,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -1598,6 +1888,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -1635,6 +1935,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -1672,6 +1982,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -1709,6 +2029,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -1746,6 +2076,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -1783,6 +2123,16 @@
           <t>文脈規定・言い換え</t>
         </is>
       </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -1820,6 +2170,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -1857,6 +2217,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>人称代名詞＝文脈非一意（わたし/かれ等）。作問困難。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -1894,6 +2264,16 @@
           <t>文脈規定・聞き取り</t>
         </is>
       </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>漢字読み・表記</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>読み:「りんごを 四つ 買いました」下線=四つ→よっつ（誤:よつ/しつ/よんつ）／表記:「みかんが よっつ」→四つ（誤:五つ/六つ/九つ）</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -1931,6 +2311,16 @@
           <t>漢字読み・表記</t>
         </is>
       </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>△漢字読み・表記</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>熟語で可:「いま 三時 です」→さんじ／表記 さんじ→三時（接辞単独ゆえ薄い）</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -1968,6 +2358,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -2005,6 +2405,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -2042,6 +2452,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -2079,6 +2499,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -2116,6 +2546,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -2153,6 +2593,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -2190,6 +2640,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>漢字読み・表記</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>読み:「へやに 誰か いますか」下線=誰か→だれか（誤:どこか/なにか/いつか）／表記:「だれか います」→誰か</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -2227,6 +2687,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -2264,6 +2734,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -2301,6 +2781,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -2338,6 +2828,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -2375,6 +2875,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -2412,6 +2922,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -2449,6 +2969,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -2486,6 +3016,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -2523,6 +3063,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -2560,6 +3110,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>疑問詞＝文脈非一意（どこ/だれ等と競合）。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -2597,6 +3157,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>頻度副詞＝言い換え△（たいてい/よく）だが非一意になりやすい。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -2634,6 +3204,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -2641,9 +3221,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -2669,6 +3249,16 @@
       <c r="G61" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -2678,9 +3268,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -2706,6 +3296,16 @@
       <c r="G62" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -2715,9 +3315,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -2743,6 +3343,16 @@
       <c r="G63" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -2752,9 +3362,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -2780,6 +3390,16 @@
       <c r="G64" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -2789,9 +3409,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -2817,6 +3437,16 @@
       <c r="G65" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -2856,6 +3486,16 @@
           <t>文脈規定・言い換え</t>
         </is>
       </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -2863,9 +3503,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -2891,6 +3531,16 @@
       <c r="G67" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H67" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -2900,9 +3550,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -2928,6 +3578,16 @@
       <c r="G68" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -2937,9 +3597,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -2965,6 +3625,16 @@
       <c r="G69" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -2974,9 +3644,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -3002,6 +3672,16 @@
       <c r="G70" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H70" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3011,9 +3691,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -3039,6 +3719,16 @@
       <c r="G71" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3048,9 +3738,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -3076,6 +3766,16 @@
       <c r="G72" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H72" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3085,9 +3785,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -3113,6 +3813,16 @@
       <c r="G73" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H73" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3122,9 +3832,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -3150,6 +3860,16 @@
       <c r="G74" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H74" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3189,6 +3909,16 @@
           <t>文脈規定・言い換え</t>
         </is>
       </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -3196,9 +3926,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -3224,6 +3954,16 @@
       <c r="G76" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H76" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3263,6 +4003,16 @@
           <t>文脈規定・言い換え</t>
         </is>
       </c>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>△漢字読み・表記</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>熟語で可:「田中様」→さま（敬称・薄い）</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -3270,9 +4020,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -3298,6 +4048,16 @@
       <c r="G78" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H78" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3307,9 +4067,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -3335,6 +4095,16 @@
       <c r="G79" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H79" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3344,9 +4114,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -3372,6 +4142,16 @@
       <c r="G80" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H80" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3381,9 +4161,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -3409,6 +4189,16 @@
       <c r="G81" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H81" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3418,9 +4208,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -3446,6 +4236,16 @@
       <c r="G82" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H82" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3455,9 +4255,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -3483,6 +4283,16 @@
       <c r="G83" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H83" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3492,9 +4302,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -3520,6 +4330,16 @@
       <c r="G84" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H84" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3529,9 +4349,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -3557,6 +4377,16 @@
       <c r="G85" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3596,6 +4426,16 @@
           <t>文脈規定・言い換え</t>
         </is>
       </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>かな接辞（〜付き）＝単独作問不可・産出も不可。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -3603,9 +4443,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -3631,6 +4471,16 @@
       <c r="G87" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H87" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3640,9 +4490,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -3668,6 +4518,16 @@
       <c r="G88" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H88" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3677,9 +4537,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -3705,6 +4565,16 @@
       <c r="G89" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H89" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3714,9 +4584,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -3742,6 +4612,16 @@
       <c r="G90" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H90" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3751,9 +4631,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -3779,6 +4659,16 @@
       <c r="G91" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H91" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3788,9 +4678,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -3816,6 +4706,16 @@
       <c r="G92" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H92" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3825,9 +4725,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -3853,6 +4753,16 @@
       <c r="G93" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H93" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3862,9 +4772,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -3890,6 +4800,16 @@
       <c r="G94" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H94" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3899,9 +4819,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -3927,6 +4847,16 @@
       <c r="G95" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H95" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3936,9 +4866,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -3964,6 +4894,16 @@
       <c r="G96" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H96" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -3973,9 +4913,9 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -4001,6 +4941,16 @@
       <c r="G97" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H97" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4010,9 +4960,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -4038,6 +4988,16 @@
       <c r="G98" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H98" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4047,9 +5007,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -4075,6 +5035,16 @@
       <c r="G99" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H99" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4084,9 +5054,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -4112,6 +5082,16 @@
       <c r="G100" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H100" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4121,9 +5101,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B101" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -4149,6 +5129,16 @@
       <c r="G101" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H101" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4158,9 +5148,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -4186,6 +5176,16 @@
       <c r="G102" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H102" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4225,6 +5225,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
@@ -4232,9 +5242,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -4260,6 +5270,16 @@
       <c r="G104" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H104" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4299,6 +5319,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -4306,9 +5336,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -4334,6 +5364,16 @@
       <c r="G106" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H106" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4343,9 +5383,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B107" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
@@ -4371,6 +5411,16 @@
       <c r="G107" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H107" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4380,9 +5430,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -4408,6 +5458,16 @@
       <c r="G108" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H108" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4447,6 +5507,16 @@
           <t>文脈規定・聞き取り</t>
         </is>
       </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>あいさつ定型＝単独作問不可。</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
@@ -4484,6 +5554,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
@@ -4491,9 +5571,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -4519,6 +5599,16 @@
       <c r="G111" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H111" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4528,9 +5618,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B112" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -4556,6 +5646,16 @@
       <c r="G112" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H112" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4565,9 +5665,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
@@ -4593,6 +5693,16 @@
       <c r="G113" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H113" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4602,9 +5712,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B114" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -4630,6 +5740,16 @@
       <c r="G114" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H114" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4639,9 +5759,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -4667,6 +5787,16 @@
       <c r="G115" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H115" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4676,9 +5806,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -4704,6 +5834,16 @@
       <c r="G116" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H116" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4743,6 +5883,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
@@ -4780,6 +5930,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -4817,6 +5977,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -4824,9 +5994,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B120" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -4852,6 +6022,16 @@
       <c r="G120" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H120" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4861,9 +6041,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B121" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
@@ -4889,6 +6069,16 @@
       <c r="G121" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H121" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4898,9 +6088,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B122" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -4926,6 +6116,16 @@
       <c r="G122" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H122" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4935,9 +6135,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
@@ -4963,6 +6163,16 @@
       <c r="G123" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H123" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -4972,9 +6182,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B124" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -5000,6 +6210,16 @@
       <c r="G124" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H124" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5009,9 +6229,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B125" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
@@ -5037,6 +6257,16 @@
       <c r="G125" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H125" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5046,9 +6276,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B126" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -5074,6 +6304,16 @@
       <c r="G126" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H126" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5083,9 +6323,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B127" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
@@ -5111,6 +6351,16 @@
       <c r="G127" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H127" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5120,9 +6370,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B128" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
@@ -5148,6 +6398,16 @@
       <c r="G128" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H128" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5157,9 +6417,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B129" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
@@ -5185,6 +6445,16 @@
       <c r="G129" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H129" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5194,9 +6464,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B130" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
@@ -5222,6 +6492,16 @@
       <c r="G130" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H130" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5231,9 +6511,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B131" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
@@ -5259,6 +6539,16 @@
       <c r="G131" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H131" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5268,9 +6558,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B132" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -5296,6 +6586,16 @@
       <c r="G132" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H132" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5331,6 +6631,16 @@
           <t>文脈規定・聞き取り</t>
         </is>
       </c>
+      <c r="H133" s="12" t="inlineStr">
+        <is>
+          <t>漢字読み・表記</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>読み:「タオルで 体を 擦る」下線=擦る→こする（誤:する/さする/ふる）／表記:「布で こする」→擦る</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -5338,9 +6648,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B134" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -5366,6 +6676,16 @@
       <c r="G134" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H134" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5375,9 +6695,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B135" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
@@ -5403,6 +6723,16 @@
       <c r="G135" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H135" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5412,9 +6742,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B136" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
@@ -5440,6 +6770,16 @@
       <c r="G136" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H136" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5449,9 +6789,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B137" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
@@ -5477,6 +6817,16 @@
       <c r="G137" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H137" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5486,9 +6836,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B138" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
@@ -5514,6 +6864,16 @@
       <c r="G138" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H138" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5523,9 +6883,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B139" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
@@ -5551,6 +6911,16 @@
       <c r="G139" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H139" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5560,9 +6930,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B140" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
@@ -5588,6 +6958,16 @@
       <c r="G140" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H140" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5597,9 +6977,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B141" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
@@ -5625,6 +7005,16 @@
       <c r="G141" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H141" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5634,9 +7024,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B142" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
@@ -5662,6 +7052,16 @@
       <c r="G142" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H142" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5671,9 +7071,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B143" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
@@ -5699,6 +7099,16 @@
       <c r="G143" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H143" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5708,9 +7118,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B144" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B144" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
@@ -5736,6 +7146,16 @@
       <c r="G144" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H144" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5775,6 +7195,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
@@ -5782,9 +7212,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B146" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B146" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
@@ -5810,6 +7240,16 @@
       <c r="G146" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H146" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5849,6 +7289,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
@@ -5856,9 +7306,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B148" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B148" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
@@ -5884,6 +7334,16 @@
       <c r="G148" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H148" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5893,9 +7353,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B149" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
@@ -5921,6 +7381,16 @@
       <c r="G149" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H149" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5930,9 +7400,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B150" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
@@ -5958,6 +7428,16 @@
       <c r="G150" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H150" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -5967,9 +7447,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B151" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B151" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
@@ -5995,6 +7475,16 @@
       <c r="G151" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H151" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -6004,9 +7494,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B152" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B152" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
@@ -6032,6 +7522,16 @@
       <c r="G152" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H152" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -6041,9 +7541,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B153" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B153" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
@@ -6069,6 +7569,16 @@
       <c r="G153" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H153" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -6078,9 +7588,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B154" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B154" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
@@ -6106,6 +7616,16 @@
       <c r="G154" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H154" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
@@ -6145,6 +7665,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>指示語（こそあど）＝文脈穴埋めが非一意（これ/それ/あれ等が同時成立）で作問不可。文脈・聞き取りが上限。</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
@@ -6182,6 +7712,16 @@
           <t>産出(語彙パズル)・聞き取り</t>
         </is>
       </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>感動詞・あいさつ＝一意な単独出題が作れない。</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
@@ -6189,9 +7729,9 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B157" s="5" t="inlineStr">
-        <is>
-          <t>2面</t>
+      <c r="B157" s="13" t="inlineStr">
+        <is>
+          <t>3面(反映済)</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
@@ -6217,6 +7757,16 @@
       <c r="G157" s="6" t="inlineStr">
         <is>
           <t>文脈規定・聞き取り</t>
+        </is>
+      </c>
+      <c r="H157" s="13" t="inlineStr">
+        <is>
+          <t>表記(カタカナ)✓反映済</t>
+        </is>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>content反映済み(→3面)。正=カタカナ／誤=紛らわしいカナ3つ（濁点・シ/ツ・ソ/ン・長音）</t>
         </is>
       </c>
     </row>
